--- a/Result/profitability/6961.xlsx
+++ b/Result/profitability/6961.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM13"/>
+  <dimension ref="A1:AM14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2081,6 +2081,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>6961</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1024</v>
+      </c>
+      <c r="D14" t="n">
+        <v>907</v>
+      </c>
+      <c r="E14" t="n">
+        <v>117</v>
+      </c>
+      <c r="F14" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-0.99%</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.81125</v>
+      </c>
+      <c r="N14" t="n">
+        <v>13.75125</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-1.031578947368421</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-4.839999999999998</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0.2980295566502462</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-1.65</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.1264367816091955</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK14" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
